--- a/Deliverables/BOM/DigiKey_BOMs/Input_Board_DigiKey.xlsx
+++ b/Deliverables/BOM/DigiKey_BOMs/Input_Board_DigiKey.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\IbrahimHyder-ReverseEngineering\Deliverables\BOM\DigiKey_BOMs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A32F0E47-2368-4D3A-BBE7-297474F2284C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E5E3317-9A69-4CB8-B248-A86DA3FFC7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
   <si>
     <t>Description</t>
   </si>
@@ -149,6 +149,9 @@
   <si>
     <t xml:space="preserve">	
 440055-2</t>
+  </si>
+  <si>
+    <t>Bill of Material (BOM) for Input Board (Ibrahim Design)</t>
   </si>
 </sst>
 </file>
@@ -254,7 +257,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -263,21 +266,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -306,21 +294,6 @@
         <color indexed="64"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -391,36 +364,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -434,6 +377,51 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -441,7 +429,50 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -451,12 +482,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -464,82 +492,105 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -852,317 +903,316 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="18"/>
-      <c r="V1" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="17"/>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="17"/>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17"/>
-      <c r="AK1" s="17"/>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="18"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
+      <c r="Y1" s="19"/>
+      <c r="Z1" s="19"/>
+      <c r="AA1" s="19"/>
+      <c r="AB1" s="19"/>
+      <c r="AC1" s="19"/>
+      <c r="AD1" s="19"/>
+      <c r="AE1" s="19"/>
+      <c r="AF1" s="19"/>
+      <c r="AG1" s="19"/>
+      <c r="AH1" s="19"/>
+      <c r="AI1" s="19"/>
+      <c r="AJ1" s="19"/>
+      <c r="AK1" s="19"/>
+      <c r="AL1" s="19"/>
+      <c r="AM1" s="19"/>
+      <c r="AN1" s="20"/>
     </row>
     <row r="2" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="Q2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="R2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="S2" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="T2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="U2" s="6" t="s">
+      <c r="U2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="V2" s="6" t="s">
+      <c r="V2" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="W2" s="6" t="s">
+      <c r="W2" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:40" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="12">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="30" t="s">
+      <c r="H3" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="31">
+      <c r="J3" s="26">
         <v>2</v>
       </c>
-      <c r="K3" s="8">
+      <c r="K3" s="6">
         <f>J3*5</f>
         <v>10</v>
       </c>
-      <c r="L3" s="8">
+      <c r="L3" s="6">
         <f>J3*1000</f>
         <v>2000</v>
       </c>
-      <c r="M3" s="8">
+      <c r="M3" s="6">
         <f>J3*5000</f>
         <v>10000</v>
       </c>
-      <c r="N3" s="32" t="s">
+      <c r="N3" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="O3" s="9">
+      <c r="O3" s="7">
         <v>0.19</v>
       </c>
-      <c r="P3" s="26">
+      <c r="P3" s="12">
         <f>O3*J3</f>
         <v>0.38</v>
       </c>
-      <c r="Q3" s="9">
+      <c r="Q3" s="7">
         <v>0.17599999999999999</v>
       </c>
-      <c r="R3" s="26">
+      <c r="R3" s="12">
         <f>Q3*K3</f>
         <v>1.7599999999999998</v>
       </c>
-      <c r="S3" s="23">
+      <c r="S3" s="10">
         <v>7.886E-2</v>
       </c>
-      <c r="T3" s="27">
+      <c r="T3" s="13">
         <f>S3*L3</f>
         <v>157.72</v>
       </c>
-      <c r="U3" s="10">
+      <c r="U3" s="8">
         <v>6.5720000000000001E-2</v>
       </c>
-      <c r="V3" s="25">
+      <c r="V3" s="11">
         <f>U3*M3</f>
         <v>657.2</v>
       </c>
-      <c r="W3" s="29" t="s">
+      <c r="W3" s="15" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="12">
-        <f>A3+1</f>
+      <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="20" t="s">
+      <c r="B4" s="27"/>
+      <c r="C4" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="22" t="s">
+      <c r="I4" s="30" t="s">
         <v>29</v>
       </c>
       <c r="J4" s="31">
         <v>1</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4" s="32">
         <f t="shared" ref="K4" si="0">J4*5</f>
         <v>5</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L4" s="33">
         <f>J4*1000</f>
         <v>1000</v>
       </c>
-      <c r="M4" s="8">
+      <c r="M4" s="33">
         <f>J4*5000</f>
         <v>5000</v>
       </c>
-      <c r="N4" s="33" t="s">
+      <c r="N4" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="O4" s="7">
+      <c r="O4" s="35">
         <v>0.58499999999999996</v>
       </c>
-      <c r="P4" s="26">
+      <c r="P4" s="36">
         <f>O4*J4</f>
         <v>0.58499999999999996</v>
       </c>
-      <c r="Q4" s="7">
+      <c r="Q4" s="35">
         <v>0.53600000000000003</v>
       </c>
-      <c r="R4" s="26">
+      <c r="R4" s="36">
         <f>Q4*K4</f>
         <v>2.68</v>
       </c>
-      <c r="S4" s="24">
+      <c r="S4" s="37">
         <v>0.51</v>
       </c>
-      <c r="T4" s="27">
+      <c r="T4" s="38">
         <f>S4*L4</f>
         <v>510</v>
       </c>
-      <c r="U4" s="10">
+      <c r="U4" s="39">
         <v>6.5720000000000001E-2</v>
       </c>
-      <c r="V4" s="25">
+      <c r="V4" s="40">
         <f>U4*M4</f>
         <v>328.6</v>
       </c>
-      <c r="W4" s="11"/>
+      <c r="W4" s="41"/>
     </row>
     <row r="5" spans="1:40" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="R5" s="4">
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="21"/>
+      <c r="N5" s="21"/>
+      <c r="O5" s="21"/>
+      <c r="R5" s="3">
         <f>SUM(R3:R4)</f>
         <v>4.4399999999999995</v>
       </c>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4">
+      <c r="S5" s="3"/>
+      <c r="T5" s="3">
         <f>SUM(T3:T4)</f>
         <v>667.72</v>
       </c>
-      <c r="V5" s="28">
+      <c r="V5" s="14">
         <f>SUM(V3:V4)</f>
         <v>985.80000000000007</v>
       </c>
     </row>
     <row r="6" spans="1:40" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="3">
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="2">
         <f>SUM(P3:P4)</f>
         <v>0.96499999999999997</v>
       </c>
-      <c r="R6" s="5">
+      <c r="R6" s="4">
         <f>R5/5</f>
         <v>0.8879999999999999</v>
       </c>
-      <c r="S6" s="5"/>
-      <c r="T6" s="5"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/Deliverables/BOM/DigiKey_BOMs/Input_Board_DigiKey.xlsx
+++ b/Deliverables/BOM/DigiKey_BOMs/Input_Board_DigiKey.xlsx
@@ -5,20 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\IbrahimHyder-ReverseEngineering\Deliverables\BOM\DigiKey_BOMs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eSpark-37\Documents\GitHub\IbrahimHyder-ReverseEngineering\Deliverables\BOM\DigiKey_BOMs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E5E3317-9A69-4CB8-B248-A86DA3FFC7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21455DD-B867-4722-8132-BBE6498C34F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="SM_Bottom_Board" sheetId="1" r:id="rId1"/>
+    <sheet name="Input_Board" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">SM_Bottom_Board!#REF!</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Input_Board!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="52">
   <si>
     <t>Description</t>
   </si>
@@ -78,9 +78,6 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>Bill of Material (BOM) for Cole Benson</t>
-  </si>
-  <si>
     <t>Connectors</t>
   </si>
   <si>
@@ -99,24 +96,15 @@
     <t>S2B-PH-K-S(LF)(SN)</t>
   </si>
   <si>
-    <t>DC Power Receptacle Jack 2.5A 2.5mm 6.5mm SMD Power Connectors RoHS</t>
-  </si>
-  <si>
     <t>J2</t>
   </si>
   <si>
-    <t>DC-005-5A-2.5-SMT</t>
-  </si>
-  <si>
     <t>Manufacturer Part No:</t>
   </si>
   <si>
     <t>JST</t>
   </si>
   <si>
-    <t>XKB Enterprise</t>
-  </si>
-  <si>
     <t>-------------</t>
   </si>
   <si>
@@ -139,12 +127,6 @@
   </si>
   <si>
     <t>Quantity 5000</t>
-  </si>
-  <si>
-    <t>Local Suplier</t>
-  </si>
-  <si>
-    <t>part out of stock. Similar alternate has been suggested.</t>
   </si>
   <si>
     <t xml:space="preserve">	
@@ -152,6 +134,58 @@
   </si>
   <si>
     <t>Bill of Material (BOM) for Input Board (Ibrahim Design)</t>
+  </si>
+  <si>
+    <t>Test Points</t>
+  </si>
+  <si>
+    <t>SMD Test points</t>
+  </si>
+  <si>
+    <t>P1, P2, P3, P4, P5, P6</t>
+  </si>
+  <si>
+    <t>Custom(SMD)</t>
+  </si>
+  <si>
+    <t>Do Not Mount</t>
+  </si>
+  <si>
+    <t>Part out of stock. Similar alternate has been suggested.</t>
+  </si>
+  <si>
+    <t>Resistors</t>
+  </si>
+  <si>
+    <t>RES 5.1K OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>R1, R2</t>
+  </si>
+  <si>
+    <t>RMCF0603FT5K10</t>
+  </si>
+  <si>
+    <t>Stackpole Electronics</t>
+  </si>
+  <si>
+    <t>5.1K</t>
+  </si>
+  <si>
+    <t>0603 (1608 Metric)</t>
+  </si>
+  <si>
+    <t>Through Hole (2mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 
+USB-C (USB TYPE-C) USB 3.2 Gen 2 (USB 3.1 Gen 2, Superspeed + (USB 3.1)) Receptacle Connector 24 Position Surface Mount, Through Hole</t>
+  </si>
+  <si>
+    <t>632722110112</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Würth Elektronik</t>
   </si>
 </sst>
 </file>
@@ -257,7 +291,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -266,17 +300,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -309,17 +332,19 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -337,7 +362,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
@@ -352,12 +377,70 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -365,81 +448,131 @@
     </border>
     <border>
       <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
@@ -448,31 +581,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
+      <left/>
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -482,18 +596,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -501,67 +638,19 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -570,27 +659,108 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -875,15 +1045,14 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN6"/>
+  <dimension ref="A1:AN8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
     <col min="3" max="3" width="73.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.140625" customWidth="1"/>
-    <col min="5" max="5" width="25" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="4" max="5" width="22.42578125" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
     <col min="7" max="7" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.42578125" bestFit="1" customWidth="1"/>
@@ -903,328 +1072,492 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="W1" s="19"/>
-      <c r="X1" s="19"/>
-      <c r="Y1" s="19"/>
-      <c r="Z1" s="19"/>
-      <c r="AA1" s="19"/>
-      <c r="AB1" s="19"/>
-      <c r="AC1" s="19"/>
-      <c r="AD1" s="19"/>
-      <c r="AE1" s="19"/>
-      <c r="AF1" s="19"/>
-      <c r="AG1" s="19"/>
-      <c r="AH1" s="19"/>
-      <c r="AI1" s="19"/>
-      <c r="AJ1" s="19"/>
-      <c r="AK1" s="19"/>
-      <c r="AL1" s="19"/>
-      <c r="AM1" s="19"/>
-      <c r="AN1" s="20"/>
+      <c r="A1" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="25"/>
+      <c r="AB1" s="25"/>
+      <c r="AC1" s="25"/>
+      <c r="AD1" s="25"/>
+      <c r="AE1" s="25"/>
+      <c r="AF1" s="25"/>
+      <c r="AG1" s="25"/>
+      <c r="AH1" s="25"/>
+      <c r="AI1" s="25"/>
+      <c r="AJ1" s="25"/>
+      <c r="AK1" s="25"/>
+      <c r="AL1" s="25"/>
+      <c r="AM1" s="25"/>
+      <c r="AN1" s="26"/>
     </row>
     <row r="2" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="5" t="s">
+      <c r="F2" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="N2" s="5" t="s">
+      <c r="L2" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Q2" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="R2" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="S2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="U2" s="5" t="s">
+      <c r="S2" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="T2" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="U2" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="V2" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="W2" s="33" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="47">
+        <v>1</v>
+      </c>
+      <c r="B3" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="58" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="V2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:40" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" s="26">
+      <c r="I3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="10">
         <v>2</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="2">
         <f>J3*5</f>
         <v>10</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="2">
         <f>J3*1000</f>
         <v>2000</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="2">
         <f>J3*5000</f>
         <v>10000</v>
       </c>
-      <c r="N3" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="O3" s="7">
+      <c r="N3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" s="3">
         <v>0.19</v>
       </c>
-      <c r="P3" s="12">
+      <c r="P3" s="5">
         <f>O3*J3</f>
         <v>0.38</v>
       </c>
-      <c r="Q3" s="7">
+      <c r="Q3" s="3">
         <v>0.17599999999999999</v>
       </c>
-      <c r="R3" s="12">
+      <c r="R3" s="5">
         <f>Q3*K3</f>
         <v>1.7599999999999998</v>
       </c>
-      <c r="S3" s="10">
+      <c r="S3" s="3">
         <v>7.886E-2</v>
       </c>
-      <c r="T3" s="13">
+      <c r="T3" s="5">
         <f>S3*L3</f>
         <v>157.72</v>
       </c>
-      <c r="U3" s="8">
+      <c r="U3" s="37">
         <v>6.5720000000000001E-2</v>
       </c>
-      <c r="V3" s="11">
+      <c r="V3" s="38">
         <f>U3*M3</f>
         <v>657.2</v>
       </c>
-      <c r="W3" s="15" t="s">
+      <c r="W3" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:40" s="55" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="48">
+        <v>2</v>
+      </c>
+      <c r="B4" s="51"/>
+      <c r="C4" s="57" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="18" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="4" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="29" t="s">
+      <c r="F4" s="59" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="I4" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="31">
+      <c r="J4" s="20">
         <v>1</v>
       </c>
-      <c r="K4" s="32">
-        <f t="shared" ref="K4" si="0">J4*5</f>
+      <c r="K4" s="21">
+        <f t="shared" ref="K4:K6" si="0">J4*5</f>
         <v>5</v>
       </c>
-      <c r="L4" s="33">
+      <c r="L4" s="21">
         <f>J4*1000</f>
         <v>1000</v>
       </c>
-      <c r="M4" s="33">
+      <c r="M4" s="21">
         <f>J4*5000</f>
         <v>5000</v>
       </c>
-      <c r="N4" s="34" t="s">
+      <c r="N4" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" s="23">
+        <v>4.82</v>
+      </c>
+      <c r="P4" s="24">
+        <f>O4*J4</f>
+        <v>4.82</v>
+      </c>
+      <c r="Q4" s="23">
+        <v>4.4219999999999997</v>
+      </c>
+      <c r="R4" s="24">
+        <f>Q4*K4</f>
+        <v>22.11</v>
+      </c>
+      <c r="S4" s="23">
+        <v>2.9750000000000001</v>
+      </c>
+      <c r="T4" s="24">
+        <f>S4*L4</f>
+        <v>2975</v>
+      </c>
+      <c r="U4" s="30">
+        <v>2.9750000000000001</v>
+      </c>
+      <c r="V4" s="31">
+        <f>U4*M4</f>
+        <v>14875</v>
+      </c>
+      <c r="W4" s="54"/>
+    </row>
+    <row r="5" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="48">
+        <v>3</v>
+      </c>
+      <c r="B5" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="O4" s="35">
-        <v>0.58499999999999996</v>
-      </c>
-      <c r="P4" s="36">
-        <f>O4*J4</f>
-        <v>0.58499999999999996</v>
-      </c>
-      <c r="Q4" s="35">
-        <v>0.53600000000000003</v>
-      </c>
-      <c r="R4" s="36">
-        <f>Q4*K4</f>
-        <v>2.68</v>
-      </c>
-      <c r="S4" s="37">
-        <v>0.51</v>
-      </c>
-      <c r="T4" s="38">
-        <f>S4*L4</f>
-        <v>510</v>
-      </c>
-      <c r="U4" s="39">
-        <v>6.5720000000000001E-2</v>
-      </c>
-      <c r="V4" s="40">
-        <f>U4*M4</f>
-        <v>328.6</v>
-      </c>
-      <c r="W4" s="41"/>
+      <c r="E5" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" s="20">
+        <v>6</v>
+      </c>
+      <c r="K5" s="21">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="L5" s="21">
+        <f t="shared" ref="L5:L6" si="1">J5*1000</f>
+        <v>6000</v>
+      </c>
+      <c r="M5" s="21">
+        <f t="shared" ref="M5:M6" si="2">J5*5000</f>
+        <v>30000</v>
+      </c>
+      <c r="N5" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="O5" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="P5" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q5" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="R5" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="S5" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="T5" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="U5" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="V5" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="W5" s="39" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="5" spans="1:40" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="J5" s="21" t="s">
+    <row r="6" spans="1:40" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="53">
+        <v>4</v>
+      </c>
+      <c r="B6" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="12">
+        <v>2</v>
+      </c>
+      <c r="K6" s="13">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="L6" s="13">
+        <f t="shared" si="1"/>
+        <v>2000</v>
+      </c>
+      <c r="M6" s="13">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="N6" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="O6" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="P6" s="43">
+        <f>O6*J6</f>
+        <v>0.2</v>
+      </c>
+      <c r="Q6" s="14">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="R6" s="43">
+        <f t="shared" ref="R5:R6" si="3">Q6*K6</f>
+        <v>0.17</v>
+      </c>
+      <c r="S6" s="14">
+        <v>3.0500000000000002E-3</v>
+      </c>
+      <c r="T6" s="43">
+        <f t="shared" ref="T5:T6" si="4">S6*L6</f>
+        <v>6.1000000000000005</v>
+      </c>
+      <c r="U6" s="44">
+        <v>2.64E-3</v>
+      </c>
+      <c r="V6" s="45">
+        <f t="shared" ref="V5:V6" si="5">U6*M6</f>
+        <v>26.4</v>
+      </c>
+      <c r="W6" s="46"/>
+    </row>
+    <row r="7" spans="1:40" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J7" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="34"/>
+      <c r="Q7" s="34"/>
+      <c r="R7" s="35">
+        <f>SUM(R3:R6)</f>
+        <v>24.04</v>
+      </c>
+      <c r="S7" s="35"/>
+      <c r="T7" s="35">
+        <f>SUM(T3:T6)</f>
+        <v>3138.8199999999997</v>
+      </c>
+      <c r="U7" s="34"/>
+      <c r="V7" s="36">
+        <f>SUM(V3:V6)</f>
+        <v>15558.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:40" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="J8" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="21"/>
-      <c r="N5" s="21"/>
-      <c r="O5" s="21"/>
-      <c r="R5" s="3">
-        <f>SUM(R3:R4)</f>
-        <v>4.4399999999999995</v>
-      </c>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3">
-        <f>SUM(T3:T4)</f>
-        <v>667.72</v>
-      </c>
-      <c r="V5" s="14">
-        <f>SUM(V3:V4)</f>
-        <v>985.80000000000007</v>
-      </c>
-    </row>
-    <row r="6" spans="1:40" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="J6" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="2">
-        <f>SUM(P3:P4)</f>
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="R6" s="4">
-        <f>R5/5</f>
-        <v>0.8879999999999999</v>
-      </c>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="56">
+        <f>SUM(P3:P6)</f>
+        <v>5.4</v>
+      </c>
+      <c r="R8" s="1">
+        <f>R7/5</f>
+        <v>4.8079999999999998</v>
+      </c>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="V1:AN1"/>
-    <mergeCell ref="J5:O5"/>
-    <mergeCell ref="J6:O6"/>
-    <mergeCell ref="A1:U1"/>
+  <mergeCells count="4">
+    <mergeCell ref="J7:O7"/>
+    <mergeCell ref="J8:O8"/>
     <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A1:W1"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
-  <conditionalFormatting sqref="J3:M4">
-    <cfRule type="colorScale" priority="7">
+  <conditionalFormatting sqref="P8:T8">
+    <cfRule type="dataBar" priority="12">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{70EE1023-228D-423C-ADF5-29102BB53C0F}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:M3 J4:J5 K4:M6">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1235,8 +1568,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P4">
-    <cfRule type="dataBar" priority="8">
+  <conditionalFormatting sqref="P3:P4 P6">
+    <cfRule type="dataBar" priority="16">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -1249,22 +1582,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P6:T6">
-    <cfRule type="dataBar" priority="10">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{70EE1023-228D-423C-ADF5-29102BB53C0F}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R3:T4">
-    <cfRule type="dataBar" priority="11">
+  <conditionalFormatting sqref="R3:T4 R6 T6">
+    <cfRule type="dataBar" priority="18">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -1277,7 +1596,31 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V3:V4">
+  <conditionalFormatting sqref="V3:V4 V6">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R3:R4 R6">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -1289,27 +1632,44 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R3:R4">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
+  <conditionalFormatting sqref="S6">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
         <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
+        <color rgb="FFFF555A"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{C9F62DC1-0B92-4FEE-ABA1-C6D999540A46}</x14:id>
+        </ext>
+      </extLst>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="N3" r:id="rId1" xr:uid="{2C99B434-E647-41FF-A13E-715CF3A744A3}"/>
+    <hyperlink ref="N6" r:id="rId2" xr:uid="{36CC0C31-8CDB-4F04-8984-E910C7ED7E35}"/>
+    <hyperlink ref="N4" r:id="rId3" xr:uid="{E51E622B-F213-41BC-89CE-537A8707BCA8}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.30555555555555558" right="0.30555555555555558" top="0.30555555555555558" bottom="0.30555555555555558" header="0" footer="0"/>
-  <pageSetup scale="39" orientation="landscape" blackAndWhite="1" r:id="rId2"/>
+  <pageSetup scale="39" orientation="landscape" blackAndWhite="1" r:id="rId4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{70EE1023-228D-423C-ADF5-29102BB53C0F}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>P8:T8</xm:sqref>
+        </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{31993F18-4C5F-4176-9D23-BFACE9C28768}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
@@ -1321,20 +1681,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P3:P4</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{70EE1023-228D-423C-ADF5-29102BB53C0F}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF63C384"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>P6:T6</xm:sqref>
+          <xm:sqref>P3:P4 P6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{BC439CAB-0450-4930-B07F-0CD52FB2A12C}">
@@ -1347,7 +1694,20 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>R3:T4</xm:sqref>
+          <xm:sqref>R3:T4 R6 T6</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{C9F62DC1-0B92-4FEE-ABA1-C6D999540A46}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFFF555A"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>S6</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
